--- a/submission/knowledge/A09-武汉新消费导购/武汉新消费导购QA导入表.xlsx
+++ b/submission/knowledge/A09-武汉新消费导购/武汉新消费导购QA导入表.xlsx
@@ -367,6 +367,584 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省博文创网上买？</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">须知曾写现场售卖为主。以当天为准。须先预约入馆。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文创</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能进江汉关上楼吗？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外立面可看。内部开放看该点公告，不保证。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉关</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">光谷买手信？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商场综合体可以，但去黄鹤楼远。食品仍问美食顾问。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">光谷</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉口里份收费吗？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">街巷免费。住宅不要闯。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">里份</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武商内部价？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没有。看店内公示。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">折扣</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">直播九块九汉绣？</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不推荐。认准正规店或授权文创。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场买特产贵吗？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可能贵。看价签。预包装相对好带。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场店</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">带盒装热干面？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">预包装看配料和保质。现制面不适合当手信。食品细节也可问美食顾问。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">热干面礼盒</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">买到仿牌？</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12315或12345。我不追款。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">假货</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">加微信代购？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不提供。走店内或官方渠道。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">代购</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉路是景区门票吗？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是。步行街免费进入。店各自营业。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉路</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和户部巷一样吗？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是。户部巷在武昌偏过早小吃；江汉路在汉口偏购物步行。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉路</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">楚河汉街要门票吗？</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">街区通常免费进入。部分展览演出另计，问预约官。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉街</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">适合买食品手信吗？</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食品保质问美食顾问。我管文创和非食品。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉街</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">昙华林能进学校医院拍照吗？</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分是学校医院住宅，不要擅闯。街巷免费。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">昙华林</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和汉街比谁更文艺？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我不排名。功能不同：昙华林偏历史街巷小店，汉街偏商业综合。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">昙华林</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三无绣片能买吗？</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不推荐。认准保护单位渠道、正规店、博物馆授权。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工艺细节你讲吗？</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">讲解交非遗文化官。我只管在哪类店买、预算、假货原则。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉绣</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没预约能进文创店吗？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">须知曾写现场售卖，通常须先入馆。以当天为准。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省博</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">镇馆之宝同款一定有吗？</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不保证。不编网店链接。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省博</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉关是商场吗？</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">近代建筑，外立面可看。内部展览看该点公告，不保证上楼。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉关</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">里份可以进院落吗？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分仍是住区。街巷免费，住宅不要闯。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">里份</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">光谷离黄鹤楼近吗？</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">要穿城。购物可以，行程结构问规划师。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">光谷</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">现制热干面当伴手礼？</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不适合托运。预包装卤味相对好带。食品细节问美食顾问。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三座火车站特产店一样吗？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以场内公示为准。不是江汉路深度逛。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车站</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能保证全网最低吗？</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。看价签，以店内当日为准。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">价格</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文创能开发票吗？</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问店家或商户助手。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">发票</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">直播低价大师亲绣？</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不推荐。投诉12315/12345。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">假货</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">液体文创能上飞机吗？</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自行判断航司规定。我不打包。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安检</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉路晚上还开吗？</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">店各自打烊时间不同，以现场为准。可接江滩看灯。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜购</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">周黑鸭你推荐哪家分店？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食品交美食顾问。预包装原则也可问他们。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我约饭桌。</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进店预约问商户助手。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">加微信代购。</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不提供。走店内或官方渠道。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉街带小孩注意什么？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人流、水面、走失约定集合点。紧急交应急助手。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">儿童</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>